--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/50_CROSS_ROLE/valcanary_part_failure_to_po_crosswalk.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/50_CROSS_ROLE/valcanary_part_failure_to_po_crosswalk.xlsx
@@ -590,12 +590,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALEVT-2024-001</t>
+          <t>Event 2024-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -627,12 +627,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALEVT-2024-001</t>
+          <t>Event 2024-001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VALPART-FLT-009</t>
+          <t>QZ-3009</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VALPO-9000000012</t>
+          <t>PO 9001000012</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -664,12 +664,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALEVT-2024-002</t>
+          <t>Event 2024-002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALPO-9000000004</t>
+          <t>PO 9001000004</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALEVT-2024-003</t>
+          <t>Event 2024-003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006</t>
+          <t>QZ-3006</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALPO-9000000003</t>
+          <t>PO 9001000003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -738,12 +738,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALEVT-2024-003</t>
+          <t>Event 2024-003</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VALPART-UPSCARD-015</t>
+          <t>QZ-3015</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VALPO-9000000008</t>
+          <t>PO 9001000008</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -775,12 +775,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALEVT-2024-004</t>
+          <t>Event 2024-004</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VALPO-9000000002</t>
+          <t>PO 9001000002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -812,12 +812,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALEVT-2024-005</t>
+          <t>Event 2024-005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VALPART-PSU-008</t>
+          <t>QZ-3008</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VALPO-9000000010</t>
+          <t>PO 9001000010</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -849,12 +849,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VALEVT-2024-008</t>
+          <t>Event 2024-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VALPO-9000000011</t>
+          <t>PO 9001000011</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -886,12 +886,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VALEVT-2024-010</t>
+          <t>Event 2024-010</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VALPART-COUPLER-012</t>
+          <t>QZ-3012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VALPO-9000000005</t>
+          <t>PO 9001000005</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -923,12 +923,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALEVT-2024-011</t>
+          <t>Event 2024-011</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VALPO-9000000009</t>
+          <t>PO 9001000009</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
